--- a/reference/列舉定義(企劃用).xlsx
+++ b/reference/列舉定義(企劃用).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AlchemyPlanning\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\ExcelEnumSelectionTool\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56080D55-671B-4BB2-A21A-7C37DC8D330F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A85CB4-52FE-461A-A05B-EE3EFD963C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="範例" sheetId="2" r:id="rId1"/>
@@ -161,7 +161,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,6 +199,13 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -232,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -244,9 +251,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -525,14 +533,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2929DAF4-3B85-4E78-8B94-9EDA6B1D9697}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -540,7 +548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -551,7 +559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
@@ -571,19 +579,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.5703125" style="1" customWidth="1"/>
     <col min="7" max="7" width="36" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -598,7 +606,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -618,7 +626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -632,7 +640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -646,7 +654,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -660,7 +668,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -674,7 +682,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="B7" s="7"/>
       <c r="E7" s="1">
         <v>5</v>
       </c>
@@ -682,7 +691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -690,7 +699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -708,7 +717,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -725,7 +734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -739,7 +748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -753,7 +762,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -761,7 +770,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -769,7 +778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>6</v>
       </c>

--- a/reference/列舉定義(企劃用).xlsx
+++ b/reference/列舉定義(企劃用).xlsx
@@ -1,32 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\ExcelEnumSelectionTool\reference\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f85608126126f9cf/桌面/AlchemyPlanning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A85CB4-52FE-461A-A05B-EE3EFD963C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{56080D55-671B-4BB2-A21A-7C37DC8D330F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBDAE58D-4543-4231-9BD1-6F9401E017D9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="範例" sheetId="2" r:id="rId1"/>
-    <sheet name="人脈系統" sheetId="1" r:id="rId2"/>
+    <sheet name="世界地圖" sheetId="6" r:id="rId2"/>
+    <sheet name="人脈系統" sheetId="1" r:id="rId3"/>
+    <sheet name="材料" sheetId="3" r:id="rId4"/>
+    <sheet name="商店" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
   <si>
     <t>[身份]顧客</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -154,6 +168,178 @@
   </si>
   <si>
     <t>被動能力目標</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialType</t>
+  </si>
+  <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYSTAL </t>
+  </si>
+  <si>
+    <t>METAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIQUID </t>
+  </si>
+  <si>
+    <t>POWDER</t>
+  </si>
+  <si>
+    <t>[材料類型]礦石</t>
+  </si>
+  <si>
+    <t>[材料類型]晶體</t>
+  </si>
+  <si>
+    <t>[材料類型]金屬錠</t>
+  </si>
+  <si>
+    <t>[材料類型]液體</t>
+  </si>
+  <si>
+    <t>[材料類型]粉末</t>
+  </si>
+  <si>
+    <t>MortarSize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杵臼大小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>無</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>容器</t>
+  </si>
+  <si>
+    <t>輔料</t>
+  </si>
+  <si>
+    <t>泥材</t>
+  </si>
+  <si>
+    <t>聲望商品</t>
+  </si>
+  <si>
+    <t>道具類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropType</t>
+  </si>
+  <si>
+    <t>人脈系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>材料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⭣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>快速跳轉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⭣</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>現貨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跑腿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StoreType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商店類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>地圖區域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郭外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>南里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>東市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -161,7 +347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,11 +386,18 @@
       <charset val="136"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Yu Gothic"/>
+      <name val="Segoe UI Symbol"/>
       <family val="2"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="4">
@@ -236,8 +429,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -251,10 +445,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -532,15 +727,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2929DAF4-3B85-4E78-8B94-9EDA6B1D9697}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
@@ -548,7 +744,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -559,7 +755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
@@ -568,6 +764,127 @@
       </c>
       <c r="C3" s="5" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="F5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F6" location="人脈系統!A1" display="人脈系統" xr:uid="{CD4731BF-3850-4A18-A4A0-5F5D676CE5FC}"/>
+    <hyperlink ref="F7" location="材料!A1" display="材料" xr:uid="{E67EB41A-19B3-4D8F-9FCC-1C1D72D76C10}"/>
+    <hyperlink ref="F8" location="商店!A1" display="商店" xr:uid="{1FA51291-BD77-46B7-98C5-DA9565EEA988}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4AA47A-3679-410F-8218-AA87138E23DF}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" t="str">
+        <f>"["&amp;C$1&amp;"]"&amp;C3</f>
+        <v>[地圖區域]無</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" ref="B4:B7" si="0">"["&amp;C$1&amp;"]"&amp;C4</f>
+        <v>[地圖區域]郭外</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>[地圖區域]南里</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>[地圖區域]西市</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>[地圖區域]東市</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -576,22 +893,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="3.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="36" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -606,7 +923,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -626,7 +943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -640,7 +957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -654,7 +971,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -668,7 +985,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -682,8 +999,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="B7" s="7"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E7" s="1">
         <v>5</v>
       </c>
@@ -691,7 +1007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>13</v>
       </c>
@@ -699,7 +1015,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
@@ -717,7 +1033,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -734,7 +1050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -748,7 +1064,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -762,7 +1078,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -770,7 +1086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -778,12 +1094,329 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF1A98D-BA98-48A0-9CB7-A9A05B1EAFEA}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.75" customWidth="1"/>
+    <col min="5" max="5" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F5" si="0">"["&amp;G$1&amp;"]"&amp;G3</f>
+        <v>[杵臼大小]小</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>[杵臼大小]中</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>[杵臼大小]大</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8D5F142-0BD1-40BB-A8D4-324724ADC46E}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.375" customWidth="1"/>
+    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>0</v>
+      </c>
+      <c r="B3" t="str">
+        <f>"["&amp;C$1&amp;"]"&amp;C3</f>
+        <v>[道具類型]無</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" t="str">
+        <f>"["&amp;G$1&amp;"]"&amp;G3</f>
+        <v>[商店類型]無</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str">
+        <f t="shared" ref="B4:B9" si="0">"["&amp;C$1&amp;"]"&amp;C4</f>
+        <v>[道具類型]材料</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" ref="F4:F8" si="1">"["&amp;G$1&amp;"]"&amp;G4</f>
+        <v>[商店類型]現貨</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>[道具類型]容器</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>[商店類型]跑腿</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>[道具類型]輔料</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str">
+        <f t="shared" si="0"/>
+        <v>[道具類型]泥材</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>[道具類型]聲望商品</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str">
+        <f t="shared" si="0"/>
+        <v>[道具類型]資源</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
